--- a/05_Figures/F06_prediction/proteins/total/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/d_1rm_legpress/spls/c_data/results.xlsx
@@ -134,40 +134,43 @@
     <t xml:space="preserve">SOD2</t>
   </si>
   <si>
+    <t xml:space="preserve">ACP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNDC17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCY</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAMK2G</t>
   </si>
   <si>
+    <t xml:space="preserve">COL6A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC2</t>
+  </si>
+  <si>
     <t xml:space="preserve">EYA3</t>
   </si>
   <si>
-    <t xml:space="preserve">GPS1</t>
+    <t xml:space="preserve">PSMA3</t>
   </si>
   <si>
     <t xml:space="preserve">TIMM50</t>
   </si>
   <si>
-    <t xml:space="preserve">TXNDC17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL6A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCY</t>
-  </si>
-  <si>
     <t xml:space="preserve">CARM1</t>
   </si>
   <si>
-    <t xml:space="preserve">COX17</t>
+    <t xml:space="preserve">FLOT1</t>
   </si>
   <si>
     <t xml:space="preserve">GAPDHS</t>
@@ -176,79 +179,82 @@
     <t xml:space="preserve">PAK1</t>
   </si>
   <si>
+    <t xml:space="preserve">TSN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCRH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR7A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCXR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL37</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMB1</t>
   </si>
   <si>
-    <t xml:space="preserve">TSN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR7A2</t>
+    <t xml:space="preserve">SRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKRD2</t>
   </si>
   <si>
     <t xml:space="preserve">APIP</t>
   </si>
   <si>
-    <t xml:space="preserve">GALK1</t>
+    <t xml:space="preserve">CDV3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERP44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGA7</t>
   </si>
   <si>
     <t xml:space="preserve">PCBP2</t>
   </si>
   <si>
+    <t xml:space="preserve">PDCD6IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">SGCA</t>
   </si>
   <si>
-    <t xml:space="preserve">ACADSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKRD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCXR</t>
+    <t xml:space="preserve">CSTB</t>
   </si>
   <si>
     <t xml:space="preserve">DDX3X</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
     <t xml:space="preserve">EPRS1</t>
   </si>
   <si>
-    <t xml:space="preserve">ERP44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRM</t>
+    <t xml:space="preserve">NPM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCB</t>
   </si>
   <si>
     <t xml:space="preserve">ATP6V1A</t>
   </si>
   <si>
-    <t xml:space="preserve">CDV3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
+    <t xml:space="preserve">DAD1</t>
   </si>
   <si>
     <t xml:space="preserve">GPX1</t>
@@ -260,253 +266,247 @@
     <t xml:space="preserve">NT5C2</t>
   </si>
   <si>
+    <t xml:space="preserve">ACSL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHORDC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLYCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP1G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNPY2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPD52L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2B</t>
+  </si>
+  <si>
     <t xml:space="preserve">UBXN6</t>
   </si>
   <si>
-    <t xml:space="preserve">ACSL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHORDC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLYCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNPY2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAHD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPD52L2</t>
+    <t xml:space="preserve">UQCRC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFG3L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARPC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATAD3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCKDHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL6A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS15L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LXN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METTL26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICOS13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSRB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTIF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFS4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXSR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PITHD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMPCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNTB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARDBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIGAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2V1</t>
   </si>
   <si>
     <t xml:space="preserve">UBE3A</t>
   </si>
   <si>
     <t xml:space="preserve">UQCRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACACB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFG3L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGMAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP1G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARPC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAD3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL6A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS15L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMFB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPUL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KYAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LXN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METTL26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICOS13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSRB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYOZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OXSR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKFB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PITHD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMPCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMIM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNTB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TALDO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TARDBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIGAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2V1</t>
   </si>
   <si>
     <t xml:space="preserve">UQCRFS1</t>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.38007401996969</v>
+        <v>-1.40790745116025</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.699786069709222</v>
+        <v>-0.580579609884938</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -929,29 +929,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.38007401996969</v>
+        <v>-1.40790745116025</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.699786069709222</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.796019900497512</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.930348258706468</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.751649816219913</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.814151428466373</v>
-      </c>
+        <v>-0.580579609884938</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -975,2206 +967,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.471281789151106</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.233043529828393</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.814056432274887</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.935497912475163</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.34637636432685</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.838321424362955</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.53105441525708</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.565080960149626</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0289354172707283</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-2.38024384809153</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.550480378604458</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.708003467873494</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.140703165290687</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.0939895609096459</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.721232485322079</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.45037661185849</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.772291094852283</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-1.48075192711587</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.24699936176988</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.399619405132453</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.0417132149852755</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.215792700937416</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.85594249529748</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.72401538374604</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.199059048654492</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-1.54589465964774</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.36876647384807</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.763885380327715</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.379186956658108</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.292297855319929</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.545084891894063</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.372433669914751</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-2.26111567120559</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.0890479839744376</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.616550745534892</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.314463924668273</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-3.04580123269907</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.604559336311236</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.339186299865973</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.37370656214921</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-2.26189242196952</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.151544758702121</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.263652137561154</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-2.44633961871637</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.00636806083520591</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-1.39333065325961</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-1.07977254971935</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-2.72199250217553</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.666435661751445</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1.10047622538914</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.908362119228261</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-2.14642320411625</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.225416724501863</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.0371022649795928</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.48821468217813</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.59911887903267</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.0600228223819</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.169982995154982</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.901987525353126</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-1.23375435749265</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-1.12893922281745</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1.98953445616617</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.288997643185887</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.670979540145733</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.277683998705731</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.382145610925038</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.14199732861504</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.383026105340864</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.21059073988907</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-1.39786224530176</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.603121746749709</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.701464718566781</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.06088529134701</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.485338285820866</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.653334736287147</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.142152689190157</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.927438056140114</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.75119089998524</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0.148711556743694</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-1.1607517147515</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.313070021834937</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-1.05316205271458</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.218870887475934</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.463040787619623</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.901480503047186</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.0678895109738546</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.437424718405421</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-1.57703701471144</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-1.47264221427371</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.75664889006277</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.543620332648867</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0.100780162769961</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0.302633492810343</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.211505254435999</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.374368274063711</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.362888183244362</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.177694105536003</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-2.69547557547587</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-1.24204992318088</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.74563977198126</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0.335953029279654</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-1.5868642107498</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.258474615534731</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-3.26972982455495</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.244806075671845</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.18315622252734</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.032713686056381</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.703835467084995</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-3.87160471700295</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.468124953933601</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.61030055557927</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.25649051863295</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.31876308744122</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.674013053542614</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.038688563721712</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.40760873590986</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.70869274542118</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.432933789718466</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.38117914781181</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0.563047965320514</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-1.26668430257694</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.299411406240432</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-3.07417604492801</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-1.13146306788588</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.556989345186091</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-2.30706395094897</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-1.00836108153279</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.92330976002554</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>0.403734504664725</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0.44829857589741</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.823383596893604</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>0.569138922814275</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0.403446120973249</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.16857897569782</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.475926283354531</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.0395123156903343</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.434074312235238</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0.0149143022655842</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.109112155229551</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.03211952923273</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.968069799211639</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0.0396444816692382</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.503493228459478</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-1.20743774953017</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0.0601127150828012</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.1240585534396</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.29778935719456</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.175534909778775</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-2.19295677249262</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.727300552623159</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.49348110455811</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-2.38284375292015</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.277943456693851</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-1.08849499085301</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.2473885091148</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.0128551832661772</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-1.63616172719721</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.05021677815799</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.350435821761958</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.525799569820551</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.0220098438771757</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.80177340679333</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-2.11104170476394</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.995750159956905</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.579788272613498</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.621831022221041</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-1.53425167752512</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>0.0208845738486436</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.29756365085752</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.69392713809978</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.46235484371396</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0.0671872096432947</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-2.50054374552501</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.376863775505331</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.15469749902231</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.667696787865623</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-1.38107614338455</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.141384311316732</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-1.55253082098068</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.234232817036075</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-1.19721069242291</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>0.206584694434039</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-1.18741380041344</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-1.48690758805925</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.025413966133789</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.562301024368549</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.984669979008364</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.596965315069748</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.215965297573674</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.0429984975254146</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.450941221347507</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.615860732120386</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.89537768176436</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.094920684541427</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.371437696751115</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.05655031756371</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.613942171480184</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.154450500769352</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>0.105790578810662</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-1.65158988972704</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3217,7 +1009,7 @@
         <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>46.9420024725877</v>
+        <v>46.7824966227071</v>
       </c>
     </row>
     <row r="3">
@@ -3234,7 +1026,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>41.1044001765378</v>
+        <v>42.6319801248046</v>
       </c>
     </row>
     <row r="4">
@@ -3251,7 +1043,7 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>20.1319489085143</v>
+        <v>23.2485712434912</v>
       </c>
     </row>
     <row r="5">
@@ -3268,7 +1060,7 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>71.824297076424</v>
+        <v>75.1820961266553</v>
       </c>
     </row>
     <row r="6">
@@ -3285,7 +1077,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>91.1960338416762</v>
+        <v>89.7456524496056</v>
       </c>
     </row>
     <row r="7">
@@ -3302,7 +1094,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>47.5672991819527</v>
+        <v>41.6423180414757</v>
       </c>
     </row>
     <row r="8">
@@ -3319,7 +1111,7 @@
         <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>28.8198314939295</v>
+        <v>28.3171403098321</v>
       </c>
     </row>
     <row r="9">
@@ -3336,7 +1128,7 @@
         <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>42.7507955259121</v>
+        <v>41.7262265630156</v>
       </c>
     </row>
     <row r="10">
@@ -3353,7 +1145,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>65.758717700559</v>
+        <v>66.7722208751015</v>
       </c>
     </row>
     <row r="11">
@@ -3370,7 +1162,7 @@
         <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>26.1081161991932</v>
+        <v>16.3172053139842</v>
       </c>
     </row>
     <row r="12">
@@ -3387,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>18.8245930134472</v>
+        <v>19.2098720294678</v>
       </c>
     </row>
     <row r="13">
@@ -3404,7 +1196,7 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>54.2084497064396</v>
+        <v>53.0331664089658</v>
       </c>
     </row>
     <row r="14">
@@ -3421,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>65.4946476226274</v>
+        <v>65.3704388913753</v>
       </c>
     </row>
     <row r="15">
@@ -3438,7 +1230,7 @@
         <v>89</v>
       </c>
       <c r="E15" t="n">
-        <v>21.866595112624</v>
+        <v>17.8849777855716</v>
       </c>
     </row>
   </sheetData>
@@ -3480,10 +1272,10 @@
         <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="3">
@@ -3565,10 +1357,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -3582,10 +1374,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="9">
@@ -3667,10 +1459,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -3684,10 +1476,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="15">
@@ -3888,10 +1680,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>0.428571428571429</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
@@ -3905,10 +1697,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.428571428571429</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
@@ -4245,10 +2037,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="48">
@@ -4347,10 +2139,10 @@
         <v>88</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="54">
@@ -4364,10 +2156,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="55">
@@ -4381,10 +2173,10 @@
         <v>90</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="56">
@@ -4517,10 +2309,10 @@
         <v>98</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="64">
@@ -4534,10 +2326,10 @@
         <v>99</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="65">

--- a/05_Figures/F06_prediction/proteins/total/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/d_1rm_legpress/spls/c_data/results.xlsx
@@ -932,7 +932,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.40790745116025</v>
@@ -940,10 +940,18 @@
       <c r="I3" t="n">
         <v>-0.580579609884938</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.825870646766169</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.845771144278607</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.743738684852384</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.806546661610694</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -967,6 +975,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.335514836862516</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.431067661042601</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.746237312142256</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.728847337160315</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.332662498377012</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.626077732217921</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.25590970606639</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.450301063502417</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.097277789937953</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-2.03425387495384</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.603292382535958</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.709833884801273</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0307760986754435</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.000389445522416487</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.674025133551182</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.21314857428657</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.556460173866715</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.26570220457154</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.27630299354778</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.206743491480741</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.246193137968421</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.305293795279807</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.704722474798531</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.7615423927448</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0463005020010918</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.59311431089125</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.08453008063732</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.589706292761573</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.428961214268738</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.247491264765228</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.656401133534615</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.399580522381793</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-2.17601178037166</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.118759736146665</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.57307940731626</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.174589927016285</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-2.84775419781709</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.311381912838193</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.0351200716464033</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.15916031819357</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-2.17108647106017</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.191728383944944</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.343953574345937</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-2.38018019893324</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0177557883427452</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.56221926991636</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.994672459749901</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-3.94244010243</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.607718940453714</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.0922934491315</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.961370299954633</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-2.0847561660927</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.19583030605844</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.0520342118710817</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.20542522895176</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.61599996226045</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.1467479211013</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.138950810690835</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.994428848549673</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.13945967199051</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.06433264906076</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.57500751682691</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.220122847289971</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.744487455163382</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.332665978943684</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.456638541489726</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.101763945691242</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.385064486326493</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.09434121041484</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.40598913851422</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.18048009232688</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.658947787027372</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.17069865705666</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.737183360850944</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.607094235813543</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.14277038943767</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.36935858210971</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.65226044628684</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.03270185951735</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.79250431903468</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.452054912262263</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.960126311472961</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.218135284045235</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.490598408285069</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.834598010796835</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.213930107641578</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.439537481015104</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-1.38454335047604</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.50192249004902</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.95944362407605</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.404797271902812</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.0073310116471208</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.535746502074981</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.447593722123663</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.498065419858242</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.274003785864512</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.168345289840003</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-2.88264552809502</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.20274622804674</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.73692253048629</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.683817303386232</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-1.4265746296951</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.184524960839528</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-3.1171217451587</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.289277998199229</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.12168174717866</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.14295385242915</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.64205742621337</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-3.53404859687899</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.600832643842311</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.666394933078521</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.349678761672634</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.150625064047585</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.984098198521104</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.0314723363544642</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.42959636027127</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.06104069342007</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.446953917124576</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.26006414621914</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.579995301971278</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.46088119853366</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.189302633187398</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-2.88047143825602</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-1.41129936027243</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.40929201085717</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-2.15574841473059</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.691350806719767</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.832297703653045</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31896801967439</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.496540012930365</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.748518191920962</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.543322776816076</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.450361038593592</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.04992099702053</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.662653461621082</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.111339542579627</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.460508910465367</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.0656907533844282</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.106421726753709</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.894305863606973</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-1.0589946057326</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.0707163281697858</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.779804142554287</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.928252291095861</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.200446361639998</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.39398614098871</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.502848555721173</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.277078010797204</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-2.20316536465025</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.698438598290479</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.3879636461871</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-2.40620709737213</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.0676275699117033</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.20259415218966</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.59976261216648</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.0245120054521673</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.51975582277267</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.17828090617888</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.337941798472375</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.503984715070646</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.0566718725064954</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.904138394789461</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-2.0900669287301</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1.07278896477283</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.580557875102376</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.06842356086715</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1.62012907304075</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.00842602548636306</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.172674180505855</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.388763030220404</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.38822844061652</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.0661453732397561</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-2.34172771649629</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.475659927780064</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.116483922638077</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.652012296761771</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.23947186605125</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.27942375534273</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-1.68150655528613</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.111365603878925</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.17756405402639</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.121219458156016</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.928555554702695</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.61020253879867</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.0748266485265662</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.370785313696977</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.05895751848188</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.579254722571996</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.0807143080002702</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.43661821722883</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.389113156158482</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.70954308023217</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.80803399983228</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.0443211742668239</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.415310930535221</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.0303311300005</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.598979102156701</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.181326025257602</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.111016694945861</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.88678203206784</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
